--- a/artfynd/A 16859-2025 artfynd.xlsx
+++ b/artfynd/A 16859-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123219381</v>
+        <v>123219686</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,12 +940,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -953,21 +953,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513011</v>
+        <v>513016</v>
       </c>
       <c r="R4" t="n">
-        <v>6702358</v>
+        <v>6702423</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en yta av ca 10x10m</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123219686</v>
+        <v>123219381</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,12 +1071,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1089,16 +1084,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513016</v>
+        <v>513011</v>
       </c>
       <c r="R5" t="n">
-        <v>6702423</v>
+        <v>6702358</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>På en yta av ca 10x10m</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123218719</v>
+        <v>123219490</v>
       </c>
       <c r="B6" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,38 +1184,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512908</v>
+        <v>513031</v>
       </c>
       <c r="R6" t="n">
-        <v>6702264</v>
+        <v>6702372</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1257,7 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,6 +1282,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1284,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123219490</v>
+        <v>123218719</v>
       </c>
       <c r="B7" t="n">
-        <v>78786</v>
+        <v>79898</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,49 +1313,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513031</v>
+        <v>512908</v>
       </c>
       <c r="R7" t="n">
-        <v>6702372</v>
+        <v>6702264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,12 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,7 +1395,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16859-2025 artfynd.xlsx
+++ b/artfynd/A 16859-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123219686</v>
+        <v>123219490</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,52 +917,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513016</v>
+        <v>513031</v>
       </c>
       <c r="R4" t="n">
-        <v>6702423</v>
+        <v>6702372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +1001,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,6 +1015,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1036,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123219381</v>
+        <v>123218719</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>79898</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,57 +1046,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513011</v>
+        <v>512908</v>
       </c>
       <c r="R5" t="n">
-        <v>6702358</v>
+        <v>6702264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,12 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en yta av ca 10x10m</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123219490</v>
+        <v>123219686</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,49 +1158,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513031</v>
+        <v>513016</v>
       </c>
       <c r="R6" t="n">
-        <v>6702372</v>
+        <v>6702423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1245,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1259,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1301,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123218719</v>
+        <v>123219381</v>
       </c>
       <c r="B7" t="n">
-        <v>79898</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,38 +1289,57 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512908</v>
+        <v>513011</v>
       </c>
       <c r="R7" t="n">
-        <v>6702264</v>
+        <v>6702358</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1376,7 +1371,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1381,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en yta av ca 10x10m</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 16859-2025 artfynd.xlsx
+++ b/artfynd/A 16859-2025 artfynd.xlsx
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65933486</v>
+        <v>73601015</v>
       </c>
       <c r="B2" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gäsan-3, Dlr</t>
+          <t>Gäsan omr 13, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512712.1531702213</v>
+        <v>513082</v>
       </c>
       <c r="R2" t="n">
-        <v>6702107.146772911</v>
+        <v>6702303</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-05-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-05-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,31 +760,30 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bonnie Nilzon</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bonnie Nilzon</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73601015</v>
+        <v>123219490</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,20 +804,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gäsan omr 13, Dlr</t>
+          <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513082.0720968156</v>
+        <v>513031</v>
       </c>
       <c r="R3" t="n">
-        <v>6702302.841896697</v>
+        <v>6702372</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-16</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-16</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,83 +881,64 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123219490</v>
+        <v>123218719</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513031</v>
+        <v>512908</v>
       </c>
       <c r="R4" t="n">
-        <v>6702372</v>
+        <v>6702264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +970,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,12 +980,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +989,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,50 +1007,64 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123218719</v>
+        <v>123219381</v>
       </c>
       <c r="B5" t="n">
-        <v>79898</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512908</v>
+        <v>513011</v>
       </c>
       <c r="R5" t="n">
-        <v>6702264</v>
+        <v>6702358</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en yta av ca 10x10m</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,12 +1141,7 @@
         <v>123219686</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1277,69 +1264,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123219381</v>
+        <v>65933486</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Torpsjön, Torpsjön, Dlr</t>
+          <t>Gäsan-3, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513011</v>
+        <v>512712</v>
       </c>
       <c r="R7" t="n">
-        <v>6702358</v>
+        <v>6702107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,27 +1331,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2017-05-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På en yta av ca 10x10m</t>
+          <t>2017-05-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,12 +1351,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bonnie Nilzon</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bonnie Nilzon</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 16859-2025 artfynd.xlsx
+++ b/artfynd/A 16859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123218719</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65933486</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73601015</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123219490</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123219381</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,8 +1390,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123219686</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>